--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:56:04+00:00</t>
+    <t>2026-10-15T09:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -544,13 +544,10 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Kategori av CareTeam.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-team-category</t>
+    <t>Typ av CareTeam enligt Ineras kodverk.</t>
+  </si>
+  <si>
+    <t>https://fhir.inera.se/ig/careteam/ValueSet/typ-av-careteam-vs</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -970,6 +967,9 @@
   </si>
   <si>
     <t>Roles may sometimes be inferred by type of Practitioner.  These are relationships that hold only within the context of the care team.  General relationships should be handled as properties of the Patient resource directly.  If a participant has multiple roles within the team, then there should be multiple participants.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
@@ -1894,7 +1894,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="108.3203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.72265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3382,13 +3382,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3424,7 +3424,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3467,10 +3467,10 @@
         <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3521,7 +3521,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3530,19 +3530,19 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3553,14 +3553,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3582,13 +3582,13 @@
         <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3626,19 +3626,19 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3659,7 +3659,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3696,19 +3696,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3757,7 +3757,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3778,21 +3778,21 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3818,10 +3818,10 @@
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3872,7 +3872,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3881,19 +3881,19 @@
         <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3904,14 +3904,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3933,13 +3933,13 @@
         <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3977,19 +3977,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4010,7 +4010,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
@@ -4050,16 +4050,16 @@
         <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4108,7 +4108,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4129,21 +4129,21 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4166,16 +4166,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4225,7 +4225,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4246,21 +4246,21 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -4286,14 +4286,14 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4342,7 +4342,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4351,7 +4351,7 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>100</v>
@@ -4363,21 +4363,21 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4400,17 +4400,17 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4459,7 +4459,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4468,7 +4468,7 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>100</v>
@@ -4480,21 +4480,21 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4517,19 +4517,19 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4578,7 +4578,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4599,21 +4599,21 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4636,19 +4636,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4697,7 +4697,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4718,21 +4718,21 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4755,16 +4755,16 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4814,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4829,16 +4829,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>78</v>
@@ -4846,14 +4846,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4872,19 +4872,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4933,7 +4933,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4948,10 +4948,10 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4965,10 +4965,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4991,17 +4991,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5050,7 +5050,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5068,7 +5068,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5111,10 +5111,10 @@
         <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5165,7 +5165,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5174,19 +5174,19 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5197,14 +5197,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5226,13 +5226,13 @@
         <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5270,19 +5270,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5303,7 +5303,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5340,16 +5340,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5399,7 +5399,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5408,7 +5408,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -5420,21 +5420,21 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5457,68 +5457,68 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="R31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5527,7 +5527,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5539,21 +5539,21 @@
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5576,13 +5576,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5633,7 +5633,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5645,30 +5645,30 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5691,13 +5691,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5748,7 +5748,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5757,19 +5757,19 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5780,14 +5780,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5809,13 +5809,13 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5865,7 +5865,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5886,7 +5886,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5897,14 +5897,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5926,16 +5926,16 @@
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5984,7 +5984,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6016,10 +6016,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6045,13 +6045,13 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6077,7 +6077,7 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>168</v>
+        <v>304</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>305</v>
@@ -6101,7 +6101,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6545,7 +6545,7 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>168</v>
+        <v>304</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>336</v>
@@ -6864,10 +6864,10 @@
         <v>90</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6918,7 +6918,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6927,19 +6927,19 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6979,13 +6979,13 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7023,19 +7023,19 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC44" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC44" t="s" s="2">
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
+      <c r="AF44" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7056,7 +7056,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7152,7 +7152,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7213,10 +7213,10 @@
         <v>90</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7267,7 +7267,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7276,19 +7276,19 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7370,19 +7370,19 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC47" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC47" t="s" s="2">
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
+      <c r="AF47" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7675,10 +7675,10 @@
         <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7729,7 +7729,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7738,19 +7738,19 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7790,13 +7790,13 @@
         <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7834,19 +7834,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC51" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC51" t="s" s="2">
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
+      <c r="AF51" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7867,7 +7867,7 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8021,13 +8021,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8078,7 +8078,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8087,19 +8087,19 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8139,13 +8139,13 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8183,19 +8183,19 @@
         <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
+      <c r="AF54" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8216,7 +8216,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8370,7 +8370,7 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>402</v>
@@ -8842,13 +8842,13 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8899,7 +8899,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8908,19 +8908,19 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8960,13 +8960,13 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9004,19 +9004,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AC61" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AC61" t="s" s="2">
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AD61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE61" t="s" s="2">
+      <c r="AF61" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9037,7 +9037,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9074,7 +9074,7 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>435</v>
@@ -9193,7 +9193,7 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>442</v>
@@ -9425,7 +9425,7 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>457</v>
@@ -9743,13 +9743,13 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -9780,7 +9780,7 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>482</v>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:21:11+00:00</t>
+    <t>2026-10-15T12:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:03:42+00:00</t>
+    <t>2026-10-15T12:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:49:20+00:00</t>
+    <t>2026-10-15T13:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Mappning mellan informationsmodell och Team</t>
+    <t>Mapping: Informationsmodell - Team</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
@@ -1904,7 +1904,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="52.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="33.78515625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="39.890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.140625" customWidth="true" bestFit="true"/>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:32:05+00:00</t>
+    <t>2026-10-15T13:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:47:34+00:00</t>
+    <t>2026-10-15T13:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:54:27+00:00</t>
+    <t>2026-10-15T14:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-managing-team-careteam.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2628" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T14:04:45+00:00</t>
+    <t>2026-10-28T12:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1184,7 +1184,7 @@
     <t>Kontaktvägens tillgänglighet</t>
   </si>
   <si>
-    <t>Anger under vilka veckodagar och tider kontaktvägen är tillgänglig.</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1222,6 +1222,9 @@
     <t>Anger återkommande veckodagar och tider då kontaktvägen är tillgänglig.</t>
   </si>
   <si>
+    <t>Saknas veckodagar, tider och period är kontaktvägen tillgänglig alla dagar, hela dygnet, tills vidare.</t>
+  </si>
+  <si>
     <t>A collection of times that the {item} is available.</t>
   </si>
   <si>
@@ -1244,6 +1247,22 @@
     <t>CareTeam.telecom.extension.value[x].availableTime.extension</t>
   </si>
   <si>
+    <t>CareTeam.telecom.extension:availability.value[x].availableTime.extension:period</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.inera.se/ig/careteam/StructureDefinition/available-time-period}
+</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Datumperiod under vilken veckodagarna och tiderna gäller. Saknas perioden gäller tiderna tills vidare.</t>
+  </si>
+  <si>
     <t>CareTeam.telecom.extension:availability.value[x].availableTime.daysOfWeek</t>
   </si>
   <si>
@@ -1254,6 +1273,9 @@
   </si>
   <si>
     <t>Veckodag då kontaktvägen är tillgänglig.</t>
+  </si>
+  <si>
+    <t>Saknas veckodag gäller tiderna alla dagar i veckan.</t>
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
@@ -1309,7 +1331,7 @@
     <t>Tidpunkt då tillgängligheten börjar.</t>
   </si>
   <si>
-    <t>The timezone is expected to be specified or implied by the context this datatype is used.</t>
+    <t>Saknas starttid gäller tillgängligheten från dagens början.</t>
   </si>
   <si>
     <t>The opening time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
@@ -1331,6 +1353,9 @@
   </si>
   <si>
     <t>Tidpunkt då tillgängligheten upphör.</t>
+  </si>
+  <si>
+    <t>Saknas sluttid gäller tillgängligheten till dagens slut.</t>
   </si>
   <si>
     <t>The closing time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
@@ -1866,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO69"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.8671875" customWidth="true" bestFit="true"/>
@@ -7912,9 +7937,11 @@
       <c r="M52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7963,7 +7990,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7975,7 +8002,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7995,10 +8022,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8110,10 +8137,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8227,21 +8254,23 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="B55" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>89</v>
@@ -8250,21 +8279,19 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>394</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8288,13 +8315,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8312,7 +8339,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>185</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8324,10 +8351,10 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8342,12 +8369,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8355,13 +8382,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
@@ -8370,17 +8397,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>229</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8405,13 +8434,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>404</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8435,16 +8464,16 @@
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8459,7 +8488,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>407</v>
       </c>
@@ -8478,7 +8507,7 @@
         <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -8487,19 +8516,17 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8548,7 +8575,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8557,13 +8584,13 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8580,10 +8607,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8606,16 +8633,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>420</v>
@@ -8676,7 +8703,7 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
@@ -8697,7 +8724,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>423</v>
       </c>
@@ -8713,10 +8740,10 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
@@ -8725,7 +8752,7 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>381</v>
+        <v>416</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>425</v>
@@ -8733,9 +8760,11 @@
       <c r="M59" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8784,22 +8813,22 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
@@ -8816,10 +8845,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8830,7 +8859,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8839,19 +8868,21 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>206</v>
+        <v>381</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>172</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>173</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8899,19 +8930,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>174</v>
+        <v>436</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8920,7 +8951,7 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8931,21 +8962,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8957,17 +8988,15 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9004,31 +9033,31 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9048,21 +9077,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9071,23 +9100,21 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>435</v>
+        <v>179</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>436</v>
+        <v>180</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9123,31 +9150,31 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>185</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9156,7 +9183,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9167,10 +9194,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9193,17 +9220,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9252,7 +9281,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9282,12 +9311,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9301,7 +9330,7 @@
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
@@ -9310,16 +9339,18 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9343,13 +9374,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9367,7 +9398,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9376,33 +9407,33 @@
         <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9425,20 +9456,16 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9462,13 +9489,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>458</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9486,7 +9513,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9495,33 +9522,33 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO65" t="s" s="2">
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
         <v>464</v>
       </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9535,28 +9562,28 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9581,13 +9608,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>471</v>
+        <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9605,7 +9632,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9614,33 +9641,33 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9657,24 +9684,26 @@
         <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9698,13 +9727,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9743,21 +9772,21 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>176</v>
+        <v>481</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>176</v>
+        <v>482</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9780,15 +9809,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9837,7 +9868,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9858,21 +9889,21 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>176</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>133</v>
+        <v>176</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9883,25 +9914,25 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J69" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K69" t="s" s="2">
-        <v>487</v>
+        <v>261</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9952,13 +9983,13 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
@@ -9967,23 +9998,138 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>490</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO69">
+  <autoFilter ref="A1:AO70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9993,7 +10139,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
